--- a/data/raw/inventory/Week 24/Nexlev/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 24/Nexlev/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 24\Nexlev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A77A300A-F30A-4675-852E-13C100151B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45F9A106-E0CF-480A-BE5F-9A65B9F02CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$430</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$417</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2586" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2578" uniqueCount="309">
   <si>
     <t>SKU</t>
   </si>
@@ -921,9 +921,6 @@
     <t>Pipeline</t>
   </si>
   <si>
-    <t>In-Transit Inventory</t>
-  </si>
-  <si>
     <t>Open Order</t>
   </si>
   <si>
@@ -931,17 +928,49 @@
   </si>
   <si>
     <t>Dispatch Partner</t>
+  </si>
+  <si>
+    <t>V-03</t>
+  </si>
+  <si>
+    <t>SC-01</t>
+  </si>
+  <si>
+    <t>GS-02</t>
+  </si>
+  <si>
+    <t>SC-05</t>
+  </si>
+  <si>
+    <t>DH-01</t>
+  </si>
+  <si>
+    <t>CAP-05</t>
+  </si>
+  <si>
+    <t>CFM-01</t>
+  </si>
+  <si>
+    <t>SC-04</t>
+  </si>
+  <si>
+    <t>MR-01</t>
+  </si>
+  <si>
+    <t>HSB-04</t>
+  </si>
+  <si>
+    <t>BR-01</t>
+  </si>
+  <si>
+    <t>PB-01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1000,12 +1029,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1056,13 +1079,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1091,20 +1113,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
@@ -1590,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L430"/>
+  <dimension ref="A1:L431"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -10088,1472 +10104,1446 @@
       </c>
     </row>
     <row r="369" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A369" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B369" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C369" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I369" s="11">
-        <v>1472</v>
+      <c r="A369" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B369" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C369" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I369" s="10">
+        <v>68</v>
       </c>
       <c r="J369" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K369" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K369" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L369" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="370" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A370" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B370" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C370" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I370" s="11">
-        <v>2000</v>
+      <c r="A370" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B370" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C370" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I370" s="10">
+        <v>13</v>
       </c>
       <c r="J370" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K370" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K370" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L370" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="371" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A371" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B371" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C371" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I371" s="11">
-        <v>2000</v>
+      <c r="A371" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B371" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C371" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I371" s="10">
+        <v>39</v>
       </c>
       <c r="J371" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K371" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K371" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L371" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="372" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A372" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B372" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C372" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I372" s="11">
-        <v>2000</v>
+      <c r="A372" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B372" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C372" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I372" s="10">
+        <v>48</v>
       </c>
       <c r="J372" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K372" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K372" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L372" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="373" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A373" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B373" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C373" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I373" s="11">
-        <v>996</v>
+      <c r="A373" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B373" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C373" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I373" s="10">
+        <v>29</v>
       </c>
       <c r="J373" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K373" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K373" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L373" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="374" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A374" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B374" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C374" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I374" s="11">
-        <v>405</v>
+      <c r="A374" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B374" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I374" s="10">
+        <v>11</v>
       </c>
       <c r="J374" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K374" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K374" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L374" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="375" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A375" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B375" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="C375" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I375" s="11">
-        <v>504</v>
+      <c r="A375" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B375" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C375" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I375" s="10">
+        <v>57</v>
       </c>
       <c r="J375" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K375" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K375" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L375" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="376" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A376" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B376" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C376" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I376" s="11">
-        <v>200</v>
+      <c r="A376" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B376" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="C376" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I376" s="10">
+        <v>35</v>
       </c>
       <c r="J376" s="8" t="s">
-        <v>293</v>
-      </c>
-      <c r="K376" s="10" t="s">
-        <v>294</v>
+        <v>295</v>
+      </c>
+      <c r="K376" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L376" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="377" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A377" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B377" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="C377" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I377" s="11">
-        <v>2000</v>
+      <c r="A377" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B377" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C377" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I377" s="10">
+        <v>3</v>
       </c>
       <c r="J377" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K377" s="10" t="s">
-        <v>294</v>
+      <c r="K377" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L377" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="378" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A378" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B378" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C378" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I378" s="11">
-        <v>2000</v>
+      <c r="A378" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B378" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I378" s="10">
+        <v>36</v>
       </c>
       <c r="J378" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K378" s="10" t="s">
-        <v>294</v>
+      <c r="K378" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L378" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="379" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A379" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B379" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C379" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I379" s="12">
-        <v>1000</v>
+      <c r="A379" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B379" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C379" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I379" s="10">
+        <v>3</v>
       </c>
       <c r="J379" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K379" s="10" t="s">
-        <v>294</v>
+      <c r="K379" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L379" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="380" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A380" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B380" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C380" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I380" s="11">
-        <v>1000</v>
+      <c r="A380" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B380" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C380" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I380" s="10">
+        <v>24</v>
       </c>
       <c r="J380" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K380" s="10" t="s">
-        <v>294</v>
+      <c r="K380" s="9" t="s">
+        <v>296</v>
       </c>
       <c r="L380" s="1" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="381" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A381" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B381" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C381" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="I381" s="12">
-        <v>1002</v>
+      <c r="A381" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B381" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="C381" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I381" s="10">
+        <v>12</v>
       </c>
       <c r="J381" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="K381" s="10" t="s">
+      <c r="K381" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L381" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A382" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B382" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C382" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I382" s="10">
+        <v>8</v>
+      </c>
+      <c r="J382" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K382" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L382" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A383" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B383" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C383" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I383" s="10">
+        <v>26</v>
+      </c>
+      <c r="J383" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K383" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L383" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A384" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B384" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I384" s="10">
+        <v>7</v>
+      </c>
+      <c r="J384" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K384" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L384" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A385" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B385" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I385" s="10">
+        <v>13</v>
+      </c>
+      <c r="J385" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K385" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L385" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A386" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="B386" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I386" s="10">
+        <v>3</v>
+      </c>
+      <c r="J386" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K386" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L386" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B387" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I387" s="10">
+        <v>88</v>
+      </c>
+      <c r="J387" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K387" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L387" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A388" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B388" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I388" s="10">
+        <v>26</v>
+      </c>
+      <c r="J388" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K388" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L388" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A389" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B389" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I389" s="10">
+        <v>82</v>
+      </c>
+      <c r="J389" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K389" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L389" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A390" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B390" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I390" s="10">
+        <v>6</v>
+      </c>
+      <c r="J390" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K390" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L390" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B391" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I391" s="10">
+        <v>7</v>
+      </c>
+      <c r="J391" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K391" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L391" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A392" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B392" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I392" s="10">
+        <v>15</v>
+      </c>
+      <c r="J392" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K392" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L392" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A393" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B393" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I393" s="10">
+        <v>41</v>
+      </c>
+      <c r="J393" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K393" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L393" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A394" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B394" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I394" s="10">
+        <v>5</v>
+      </c>
+      <c r="J394" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K394" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L394" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A395" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B395" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I395" s="10">
+        <v>25</v>
+      </c>
+      <c r="J395" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K395" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L395" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="396" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A396" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="B396" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I396" s="10">
+        <v>9</v>
+      </c>
+      <c r="J396" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K396" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L396" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A397" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B397" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I397" s="10">
+        <v>13</v>
+      </c>
+      <c r="J397" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K397" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L397" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A398" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B398" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I398" s="10">
+        <v>9</v>
+      </c>
+      <c r="J398" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K398" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L398" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A399" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B399" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I399" s="10">
+        <v>47</v>
+      </c>
+      <c r="J399" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K399" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L399" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="B400" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I400" s="10">
+        <v>16</v>
+      </c>
+      <c r="J400" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K400" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L400" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A401" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B401" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I401" s="10">
+        <v>6</v>
+      </c>
+      <c r="J401" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K401" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L401" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A402" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="B402" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I402" s="10">
+        <v>6</v>
+      </c>
+      <c r="J402" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K402" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L402" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A403" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B403" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I403" s="10">
+        <v>10</v>
+      </c>
+      <c r="J403" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K403" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L403" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A404" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B404" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I404" s="10">
+        <v>94</v>
+      </c>
+      <c r="J404" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K404" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L404" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A405" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B405" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I405" s="10">
+        <v>127</v>
+      </c>
+      <c r="J405" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K405" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L405" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A406" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="B406" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I406" s="10">
+        <v>15</v>
+      </c>
+      <c r="J406" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K406" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L406" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A407" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B407" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I407" s="10">
+        <v>10</v>
+      </c>
+      <c r="J407" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K407" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L407" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A408" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B408" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="C408" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I408" s="10">
+        <v>20</v>
+      </c>
+      <c r="J408" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K408" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L408" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A409" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B409" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C409" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I409" s="10">
+        <v>16</v>
+      </c>
+      <c r="J409" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K409" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L409" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A410" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B410" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C410" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I410" s="10">
+        <v>10</v>
+      </c>
+      <c r="J410" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K410" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L410" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A411" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B411" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C411" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I411" s="10">
+        <v>8</v>
+      </c>
+      <c r="J411" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K411" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L411" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A412" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B412" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="C412" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I412" s="10">
+        <v>62</v>
+      </c>
+      <c r="J412" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K412" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L412" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A413" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B413" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C413" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I413" s="10">
+        <v>37</v>
+      </c>
+      <c r="J413" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K413" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L413" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A414" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B414" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C414" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I414" s="10">
+        <v>30</v>
+      </c>
+      <c r="J414" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K414" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L414" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A415" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B415" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I415" s="10">
+        <v>50</v>
+      </c>
+      <c r="J415" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K415" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L415" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A416" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B416" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="C416" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I416" s="10">
+        <v>9</v>
+      </c>
+      <c r="J416" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K416" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L416" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A417" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B417" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="C417" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I417" s="10">
+        <v>21</v>
+      </c>
+      <c r="J417" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="K417" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="L417" s="1" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A418" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B418" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C418" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D418" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I418" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J418" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A419" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D419" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I419" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J419" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A420" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B420" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C420" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D420" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I420" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J420" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A421" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B421" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C421" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D421" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I421" s="1">
+        <v>996</v>
+      </c>
+      <c r="J421" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A422" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D422" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="I422" s="1">
+        <v>405</v>
+      </c>
+      <c r="J422" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A423" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B423" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="C423" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D423" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I423" s="1">
+        <v>200</v>
+      </c>
+      <c r="J423" s="1" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A424" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B424" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C424" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D424" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="I424" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J424" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="L381" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="382" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A382" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B382" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C382" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I382" s="13">
-        <v>68</v>
-      </c>
-      <c r="J382" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K382" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L382" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="383" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A383" s="13" t="s">
+    </row>
+    <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A425" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B425" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C425" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D425" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I425" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J425" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A426" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D426" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I426" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J426" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="427" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A427" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B383" s="13" t="s">
+      <c r="B427" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C383" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I383" s="13">
-        <v>13</v>
-      </c>
-      <c r="J383" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K383" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L383" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="384" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A384" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B384" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C384" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I384" s="13">
-        <v>39</v>
-      </c>
-      <c r="J384" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K384" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L384" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="385" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A385" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B385" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="C385" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I385" s="13">
-        <v>48</v>
-      </c>
-      <c r="J385" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K385" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L385" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="386" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A386" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B386" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="C386" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I386" s="13">
-        <v>29</v>
-      </c>
-      <c r="J386" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K386" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L386" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="387" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A387" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B387" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="C387" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I387" s="13">
-        <v>11</v>
-      </c>
-      <c r="J387" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K387" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L387" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="388" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A388" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B388" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C388" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I388" s="13">
-        <v>57</v>
-      </c>
-      <c r="J388" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K388" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L388" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="389" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A389" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="B389" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="C389" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I389" s="13">
-        <v>35</v>
-      </c>
-      <c r="J389" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K389" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L389" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="390" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A390" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="B390" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C390" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I390" s="13">
-        <v>3</v>
-      </c>
-      <c r="J390" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K390" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L390" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="391" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A391" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B391" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="C391" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I391" s="13">
-        <v>36</v>
-      </c>
-      <c r="J391" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K391" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L391" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="392" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A392" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B392" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C392" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I392" s="13">
-        <v>3</v>
-      </c>
-      <c r="J392" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K392" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L392" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="393" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A393" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B393" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="C393" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I393" s="13">
-        <v>24</v>
-      </c>
-      <c r="J393" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K393" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L393" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="394" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A394" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B394" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="C394" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I394" s="13">
-        <v>12</v>
-      </c>
-      <c r="J394" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K394" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L394" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="395" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A395" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B395" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C395" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I395" s="13">
-        <v>8</v>
-      </c>
-      <c r="J395" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K395" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L395" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="396" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A396" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="B396" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="C396" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I396" s="13">
-        <v>26</v>
-      </c>
-      <c r="J396" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K396" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L396" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="397" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A397" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B397" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="C397" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I397" s="13">
-        <v>7</v>
-      </c>
-      <c r="J397" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K397" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L397" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="398" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A398" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B398" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C398" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I398" s="13">
-        <v>13</v>
-      </c>
-      <c r="J398" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K398" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L398" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="399" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A399" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B399" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="C399" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I399" s="13">
-        <v>3</v>
-      </c>
-      <c r="J399" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K399" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L399" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="400" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A400" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B400" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="C400" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I400" s="13">
-        <v>88</v>
-      </c>
-      <c r="J400" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K400" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L400" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="401" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A401" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B401" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C401" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I401" s="13">
-        <v>26</v>
-      </c>
-      <c r="J401" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K401" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L401" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="402" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A402" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B402" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="C402" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I402" s="13">
-        <v>82</v>
-      </c>
-      <c r="J402" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K402" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L402" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="403" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A403" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B403" s="13" t="s">
-        <v>179</v>
-      </c>
-      <c r="C403" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I403" s="13">
-        <v>6</v>
-      </c>
-      <c r="J403" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K403" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L403" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="404" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A404" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B404" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="C404" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I404" s="13">
-        <v>7</v>
-      </c>
-      <c r="J404" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K404" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L404" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="405" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A405" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B405" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="C405" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I405" s="13">
-        <v>15</v>
-      </c>
-      <c r="J405" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K405" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L405" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="406" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A406" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="B406" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="C406" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I406" s="13">
-        <v>41</v>
-      </c>
-      <c r="J406" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K406" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L406" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="407" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A407" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="B407" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C407" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I407" s="13">
-        <v>5</v>
-      </c>
-      <c r="J407" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K407" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L407" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="408" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B408" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C408" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I408" s="13">
-        <v>25</v>
-      </c>
-      <c r="J408" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K408" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L408" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="409" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A409" s="13" t="s">
+      <c r="C427" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D427" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I427" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J427" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="428" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A428" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B409" s="13" t="s">
+      <c r="B428" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C409" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I409" s="13">
-        <v>9</v>
-      </c>
-      <c r="J409" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K409" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L409" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="410" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A410" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B410" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="C410" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I410" s="13">
-        <v>13</v>
-      </c>
-      <c r="J410" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K410" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L410" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="411" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A411" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B411" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C411" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I411" s="13">
-        <v>9</v>
-      </c>
-      <c r="J411" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K411" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L411" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="412" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A412" s="13" t="s">
+      <c r="C428" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D428" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I428" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J428" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="429" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A429" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B412" s="13" t="s">
+      <c r="B429" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="C412" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I412" s="13">
-        <v>47</v>
-      </c>
-      <c r="J412" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K412" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L412" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="413" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A413" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="B413" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C413" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I413" s="13">
-        <v>16</v>
-      </c>
-      <c r="J413" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K413" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L413" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="414" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A414" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B414" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="C414" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I414" s="13">
-        <v>6</v>
-      </c>
-      <c r="J414" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K414" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L414" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="415" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A415" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="B415" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="C415" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I415" s="13">
-        <v>6</v>
-      </c>
-      <c r="J415" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K415" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L415" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="416" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A416" s="13" t="s">
+      <c r="C429" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D429" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="I429" s="1">
+        <v>1000</v>
+      </c>
+      <c r="J429" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="430" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A430" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B416" s="13" t="s">
+      <c r="B430" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C416" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I416" s="13">
-        <v>10</v>
-      </c>
-      <c r="J416" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K416" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L416" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="417" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A417" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B417" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C417" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I417" s="13">
-        <v>94</v>
-      </c>
-      <c r="J417" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K417" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L417" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="418" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A418" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="B418" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C418" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I418" s="13">
-        <v>127</v>
-      </c>
-      <c r="J418" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K418" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L418" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="419" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A419" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="B419" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C419" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I419" s="13">
-        <v>15</v>
-      </c>
-      <c r="J419" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K419" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L419" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="420" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A420" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="B420" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C420" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I420" s="13">
-        <v>10</v>
-      </c>
-      <c r="J420" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K420" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L420" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="421" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A421" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B421" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C421" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I421" s="13">
-        <v>20</v>
-      </c>
-      <c r="J421" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K421" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L421" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="422" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A422" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="B422" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I422" s="13">
-        <v>16</v>
-      </c>
-      <c r="J422" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K422" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L422" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="423" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A423" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="B423" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C423" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I423" s="13">
-        <v>10</v>
-      </c>
-      <c r="J423" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K423" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L423" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="424" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A424" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="B424" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="C424" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I424" s="13">
-        <v>8</v>
-      </c>
-      <c r="J424" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K424" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L424" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="425" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A425" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B425" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="C425" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I425" s="13">
-        <v>62</v>
-      </c>
-      <c r="J425" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K425" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L425" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="426" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A426" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B426" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="C426" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I426" s="13">
-        <v>37</v>
-      </c>
-      <c r="J426" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K426" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L426" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="427" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A427" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B427" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="C427" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I427" s="13">
-        <v>30</v>
-      </c>
-      <c r="J427" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K427" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L427" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="428" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A428" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B428" s="13" t="s">
-        <v>212</v>
-      </c>
-      <c r="C428" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I428" s="13">
-        <v>50</v>
-      </c>
-      <c r="J428" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K428" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L428" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="429" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A429" s="13" t="s">
+      <c r="C430" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D430" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="I430" s="1">
+        <v>1002</v>
+      </c>
+      <c r="J430" s="1" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="431" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A431" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B429" s="13" t="s">
+      <c r="B431" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C429" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I429" s="13">
-        <v>9</v>
-      </c>
-      <c r="J429" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K429" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L429" s="1" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="430" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A430" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B430" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="C430" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I430" s="13">
-        <v>21</v>
-      </c>
-      <c r="J430" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="K430" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="L430" s="1" t="s">
-        <v>244</v>
+      <c r="C431" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D431" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I431" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J431" s="1" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L430" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A430">
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+  <conditionalFormatting sqref="A155:A264">
+    <cfRule type="duplicateValues" dxfId="14" priority="2198"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A251:A253">
+    <cfRule type="duplicateValues" dxfId="13" priority="2195"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A265">
+    <cfRule type="duplicateValues" dxfId="12" priority="2189"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A369:A413">
+    <cfRule type="duplicateValues" dxfId="9" priority="2182"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A369:A416">
+    <cfRule type="duplicateValues" dxfId="8" priority="2180"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A417">
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="12" priority="2105"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="2106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2106" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="10" priority="1892"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="1893" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1892"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1893" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1890"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1891" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A382:A429">
-    <cfRule type="duplicateValues" dxfId="6" priority="2180"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A382:A426">
-    <cfRule type="duplicateValues" dxfId="5" priority="2182"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A377:A381">
-    <cfRule type="duplicateValues" dxfId="4" priority="2185"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A369:A373">
-    <cfRule type="duplicateValues" dxfId="3" priority="2188"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A265">
-    <cfRule type="duplicateValues" dxfId="2" priority="2189"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A251:A253">
-    <cfRule type="duplicateValues" dxfId="1" priority="2195"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A155:A264">
-    <cfRule type="duplicateValues" dxfId="0" priority="2198"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1890"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1891" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
